--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-14).xlsx
@@ -959,10 +959,10 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>40.5%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
+    <t>40.3%</t>
+  </si>
+  <si>
+    <t>20.1%</t>
   </si>
   <si>
     <t>1.9%</t>
@@ -974,7 +974,7 @@
     <t>4.7%</t>
   </si>
   <si>
-    <t>1.5%</t>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -983,16 +983,16 @@
     <t>8.0%</t>
   </si>
   <si>
-    <t>3.4%</t>
+    <t>3.3%</t>
   </si>
   <si>
     <t>4.4%</t>
   </si>
   <si>
-    <t>1092.0</t>
-  </si>
-  <si>
-    <t>889.0</t>
+    <t>1094.0</t>
+  </si>
+  <si>
+    <t>891.0</t>
   </si>
   <si>
     <t>85.0</t>
@@ -1010,7 +1010,7 @@
     <t>8.0</t>
   </si>
   <si>
-    <t>351.0</t>
+    <t>353.0</t>
   </si>
   <si>
     <t>148.0</t>
@@ -7649,7 +7649,9 @@
       <c r="N42" s="6">
         <v>34</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6">
+        <v>24</v>
+      </c>
       <c r="P42" s="7">
         <v>5.2371428571428575</v>
       </c>
@@ -7659,31 +7661,75 @@
       <c r="R42" s="8">
         <v>6.4022727272727273</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
       <c r="T42" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="U42" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-14).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 3.264,92</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 3.264,53</t>
   </si>
   <si>
     <t>37.2</t>
   </si>
   <si>
-    <t>24.3</t>
-  </si>
-  <si>
-    <t>4.84</t>
+    <t>24.2</t>
+  </si>
+  <si>
+    <t>4.83</t>
   </si>
   <si>
     <t>19.3</t>
@@ -956,10 +956,10 @@
     <t>7.9</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>40.3%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>40.6%</t>
   </si>
   <si>
     <t>20.1%</t>
@@ -10057,7 +10057,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10087,14 +10087,26 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>3193.1900000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>37</v>
+      </c>
       <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>3.3421052631578947</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.541667647058823</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.3916676470588234</v>
+      </c>
       <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.5</v>
+      </c>
       <c r="U58" s="9"/>
       <c r="V58" s="9"/>
       <c r="W58" s="9"/>
@@ -17906,7 +17918,9 @@
       <c r="N111" s="6">
         <v>3</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>3</v>
+      </c>
       <c r="P111" s="7">
         <v>6.8777666666666661</v>
       </c>
@@ -17916,31 +17930,75 @@
       <c r="R111" s="8">
         <v>2.3166666666666669</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-14).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 3.264,53</t>
-  </si>
-  <si>
-    <t>37.2</t>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R$ 3.256,41</t>
+  </si>
+  <si>
+    <t>37.0</t>
   </si>
   <si>
     <t>24.2</t>
@@ -950,19 +950,19 @@
     <t>4.83</t>
   </si>
   <si>
-    <t>19.3</t>
+    <t>19.4</t>
   </si>
   <si>
     <t>7.9</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>40.6%</t>
-  </si>
-  <si>
-    <t>20.1%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>41.0%</t>
+  </si>
+  <si>
+    <t>19.8%</t>
   </si>
   <si>
     <t>1.9%</t>
@@ -980,37 +980,37 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>8.0%</t>
+    <t>7.8%</t>
   </si>
   <si>
     <t>3.3%</t>
   </si>
   <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>1094.0</t>
-  </si>
-  <si>
-    <t>891.0</t>
-  </si>
-  <si>
-    <t>85.0</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>209.0</t>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>1103.0</t>
+  </si>
+  <si>
+    <t>901.0</t>
+  </si>
+  <si>
+    <t>86.0</t>
+  </si>
+  <si>
+    <t>13.0</t>
+  </si>
+  <si>
+    <t>215.0</t>
   </si>
   <si>
     <t>64.0</t>
   </si>
   <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>353.0</t>
+    <t>9.0</t>
+  </si>
+  <si>
+    <t>354.0</t>
   </si>
   <si>
     <t>148.0</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,14 +2239,26 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="5">
+        <v>6205.1000000000004</v>
+      </c>
+      <c r="N6" s="6">
+        <v>68</v>
+      </c>
       <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="P6" s="7">
+        <v>5.1141409090909091</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15.087907843137254</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.1287588235294117</v>
+      </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
+      <c r="T6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -4907,7 +4919,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4937,14 +4949,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>2713.7199999999998</v>
+      </c>
+      <c r="N24" s="6">
+        <v>32</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.0204290322580647</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>19.833333333333332</v>
+      </c>
+      <c r="R24" s="8">
+        <v>9.7595238095238095</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6731,7 +6755,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6761,35 +6785,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>2867.46</v>
+      </c>
+      <c r="N36" s="6">
+        <v>35</v>
+      </c>
+      <c r="O36" s="6">
+        <v>24</v>
+      </c>
+      <c r="P36" s="7">
+        <v>4.9752371428571429</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>15.629166666666668</v>
+      </c>
+      <c r="R36" s="8">
+        <v>3.5270833333333336</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7034,7 +7116,7 @@
         <v>8.081818181818182</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.40909090909090912</v>
@@ -9020,7 +9102,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9050,35 +9132,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>659.10000000000002</v>
+      </c>
+      <c r="N51" s="6">
+        <v>5</v>
+      </c>
+      <c r="O51" s="6">
+        <v>2</v>
+      </c>
+      <c r="P51" s="7">
+        <v>6.6699999999999999</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>37.225000000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>22.875</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -10093,7 +10233,9 @@
       <c r="N58" s="6">
         <v>37</v>
       </c>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>34</v>
+      </c>
       <c r="P58" s="7">
         <v>3.3421052631578947</v>
       </c>
@@ -10103,31 +10245,75 @@
       <c r="R58" s="8">
         <v>7.3916676470588234</v>
       </c>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9">
         <v>0.5</v>
       </c>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.20588235294117646</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.029411764704999999</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -14676,7 +14862,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14704,14 +14890,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>2645.1300000000001</v>
+      </c>
+      <c r="N89" s="6">
+        <v>25</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>4.5839999999999996</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>20.092588888888891</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.0222222222222221</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.22222222222222221</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -25005,7 +25203,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25035,35 +25233,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2937.9299999999998</v>
+      </c>
+      <c r="N158" s="6">
+        <v>28</v>
+      </c>
+      <c r="O158" s="6">
+        <v>28</v>
+      </c>
+      <c r="P158" s="7">
+        <v>5.0994241379310346</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>19.472024999999999</v>
+      </c>
+      <c r="R158" s="8">
+        <v>7.7950629629629633</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -28158,7 +28414,9 @@
       <c r="N179" s="6">
         <v>54</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>22</v>
+      </c>
       <c r="P179" s="7">
         <v>5.6786169811320759</v>
       </c>
@@ -28168,31 +28426,75 @@
       <c r="R179" s="8">
         <v>1.6878772727272726</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.59090909090909094</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
